--- a/output/pdf_financials_xlsx/SIQ.H.xlsx
+++ b/output/pdf_financials_xlsx/SIQ.H.xlsx
@@ -970,7 +970,7 @@
         <v>-0.009138</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.855371</v>
+        <v>-0.855371</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.855371</v>
@@ -1158,7 +1158,7 @@
         <v>-0.009138</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.855371</v>
+        <v>-0.855371</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.855371</v>
@@ -1269,7 +1269,7 @@
         <v>-0.009138</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.855371</v>
+        <v>-0.855371</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.855371</v>
@@ -1431,7 +1431,7 @@
         <v>-0.009138</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.855371</v>
+        <v>-0.855371</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.855371</v>
@@ -1505,7 +1505,7 @@
         <v>-0.009138</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.855371</v>
+        <v>-0.855371</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.855371</v>
@@ -1599,7 +1599,7 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -3930,31 +3930,31 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.014497</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.151238</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.176042</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.195269</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.195846</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.195846</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.195846</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.195846</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.195846</v>
       </c>
     </row>
     <row r="93">
@@ -6072,7 +6072,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -6390,7 +6394,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -6850,7 +6858,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -7448,7 +7460,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -7716,7 +7732,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -8442,7 +8462,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -8894,7 +8918,11 @@
           <t>Reserves 3</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -21137,7 +21165,7 @@
         </is>
       </c>
       <c r="F241" s="5" t="n">
-        <v>0.855371</v>
+        <v>-0.855371</v>
       </c>
       <c r="G241" s="5" t="n">
         <v>-0.855371</v>

--- a/output/pdf_financials_xlsx/SIQ.H.xlsx
+++ b/output/pdf_financials_xlsx/SIQ.H.xlsx
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.018724</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>-0.855371</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.855371</v>
+        <v>-0.836647</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.051</v>
@@ -1508,7 +1508,7 @@
         <v>-0.855371</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.855371</v>
+        <v>-0.836647</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.051</v>
@@ -1709,22 +1709,22 @@
         <v>0.026908</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.020575</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.020637</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.002291</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.005359</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.07643</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.043676</v>
       </c>
     </row>
     <row r="35">
@@ -1783,22 +1783,22 @@
         <v>0.026908</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.020575</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.020637</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.002291</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.005359</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.07643</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.043676</v>
       </c>
     </row>
     <row r="37">
@@ -2227,16 +2227,16 @@
         <v>0.007082</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.023175</v>
+        <v>0.0026</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.023237</v>
+        <v>0.0026</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.002291</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.005359</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -20564,7 +20564,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">

--- a/output/pdf_financials_xlsx/SIQ.H.xlsx
+++ b/output/pdf_financials_xlsx/SIQ.H.xlsx
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.00105</v>
+        <v>0.046627</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -1514,7 +1514,7 @@
         <v>-1.051</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.43239</v>
+        <v>-0.386813</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.029855</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.046627</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -10988,7 +10988,11 @@
           <t>Depreciation – right-of-use assets</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SIQ.H.xlsx
+++ b/output/pdf_financials_xlsx/SIQ.H.xlsx
@@ -640,10 +640,10 @@
         <v>0.032007</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.241749</v>
+        <v>0.2964</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.295449</v>
+        <v>0.355449</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.069922</v>
@@ -9546,7 +9546,11 @@
           <t>Shares issued for private placement</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -19840,7 +19844,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
